--- a/aircraft/reports/sightings-over-time-daily.xlsx
+++ b/aircraft/reports/sightings-over-time-daily.xlsx
@@ -8180,7 +8180,7 @@
         <v>45900</v>
       </c>
       <c r="B968" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -15930,7 +15930,7 @@
         <v>45900</v>
       </c>
       <c r="B968" t="n">
-        <v>44.85714285714285</v>
+        <v>45.57142857142857</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-daily.xlsx
+++ b/aircraft/reports/sightings-over-time-daily.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B968"/>
+  <dimension ref="A1:B969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8181,6 +8181,14 @@
       </c>
       <c r="B968" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B969" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8194,7 +8202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B968"/>
+  <dimension ref="A1:B969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15933,6 +15941,14 @@
         <v>45.57142857142857</v>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B969" t="n">
+        <v>37.85714285714285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aircraft/reports/sightings-over-time-daily.xlsx
+++ b/aircraft/reports/sightings-over-time-daily.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B969"/>
+  <dimension ref="A1:B968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8180,14 +8180,6 @@
         <v>45900</v>
       </c>
       <c r="B968" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="969">
-      <c r="A969" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B969" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8202,7 +8194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B969"/>
+  <dimension ref="A1:B968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15938,15 +15930,7 @@
         <v>45900</v>
       </c>
       <c r="B968" t="n">
-        <v>45.57142857142857</v>
-      </c>
-    </row>
-    <row r="969">
-      <c r="A969" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B969" t="n">
-        <v>37.85714285714285</v>
+        <v>44.85714285714285</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-daily.xlsx
+++ b/aircraft/reports/sightings-over-time-daily.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B968"/>
+  <dimension ref="A1:B970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8180,6 +8180,22 @@
         <v>45900</v>
       </c>
       <c r="B968" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B969" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B970" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8194,7 +8210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B968"/>
+  <dimension ref="A1:B970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15930,7 +15946,23 @@
         <v>45900</v>
       </c>
       <c r="B968" t="n">
-        <v>44.85714285714285</v>
+        <v>45.57142857142857</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B969" t="n">
+        <v>37.85714285714285</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B970" t="n">
+        <v>37.71428571428572</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-daily.xlsx
+++ b/aircraft/reports/sightings-over-time-daily.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B970"/>
+  <dimension ref="A1:B971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8197,6 +8197,14 @@
       </c>
       <c r="B970" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B971" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -8210,7 +8218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B970"/>
+  <dimension ref="A1:B971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15965,6 +15973,14 @@
         <v>37.71428571428572</v>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B971" t="n">
+        <v>10.14285714285714</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aircraft/reports/sightings-over-time-daily.xlsx
+++ b/aircraft/reports/sightings-over-time-daily.xlsx
@@ -8204,7 +8204,7 @@
         <v>45905</v>
       </c>
       <c r="B971" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -15978,7 +15978,7 @@
         <v>45905</v>
       </c>
       <c r="B971" t="n">
-        <v>10.14285714285714</v>
+        <v>11.85714285714286</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-daily.xlsx
+++ b/aircraft/reports/sightings-over-time-daily.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B971"/>
+  <dimension ref="A1:B972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8205,6 +8205,14 @@
       </c>
       <c r="B971" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B972" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -8218,7 +8226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B971"/>
+  <dimension ref="A1:B972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15981,6 +15989,14 @@
         <v>11.85714285714286</v>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B972" t="n">
+        <v>8.857142857142858</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
